--- a/Excel/Sales-Report.xlsx
+++ b/Excel/Sales-Report.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books-and-tutorials\Excel-From-Youtube\ExcelExamples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15186008-54E4-420B-9E8D-8D3B6BB7DBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B33EE9F-60DE-44E3-AD66-163A99005047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="11" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="53">
   <si>
     <t>Product Code</t>
   </si>
@@ -176,6 +180,24 @@
   <si>
     <t>Last Name</t>
   </si>
+  <si>
+    <t>Sum of all items</t>
+  </si>
+  <si>
+    <t>Sum of items valued at more than 50$</t>
+  </si>
+  <si>
+    <t>Sum of items valued at 50$ or less</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Sale Price</t>
+  </si>
 </sst>
 </file>
 
@@ -305,7 +327,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -314,6 +336,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="0" xfId="44" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -362,7 +392,36 @@
     <cellStyle name="Hyperlink" xfId="42" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -373,6 +432,3453 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Sales-Report.xlsx]Sheet4!PivotTable3</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Barns</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Hernandez</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Johnson</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Smith</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6003.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2410.7000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3035.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5661.0999999999985</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-68CB-4393-9DF4-D2B3A893B70B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>252412</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD6A96B-9192-823A-2190-FDB579260B8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jafar" refreshedDate="46168.169895254628" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="171" xr:uid="{6FDF2314-DDE6-4374-808F-3819216022F0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K172" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="Month" numFmtId="14">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Transaction Number" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1171"/>
+    </cacheField>
+    <cacheField name="Product Code" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1109" maxValue="9822"/>
+    </cacheField>
+    <cacheField name="Product Description" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Store Cost" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3" maxValue="344"/>
+    </cacheField>
+    <cacheField name="Sale Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7" maxValue="502"/>
+    </cacheField>
+    <cacheField name="Profit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.9999999999999991" maxValue="158"/>
+    </cacheField>
+    <cacheField name="Commision 10% for items less than 50$. 20% for items more than 50$" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.29999999999999993" maxValue="31.6"/>
+    </cacheField>
+    <cacheField name="First Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Last Name" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Barns"/>
+        <s v="Hernandez"/>
+        <s v="Smith"/>
+        <s v="Johnson"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sale Location" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="171">
+  <r>
+    <s v="Jan"/>
+    <n v="1001"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1002"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1003"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1004"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1005"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1006"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1007"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1008"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1009"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1010"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1011"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1012"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1013"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1014"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1015"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Jan"/>
+    <n v="1016"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1017"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1018"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1019"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1020"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1021"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1022"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1023"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1024"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1025"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1026"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1027"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1028"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1029"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1030"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1031"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1032"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1033"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Feb"/>
+    <n v="1034"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1035"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1036"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1037"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1038"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1039"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1040"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1041"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1042"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1043"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1044"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1045"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1046"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1047"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Mar"/>
+    <n v="1048"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1049"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1050"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1051"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1052"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1053"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1054"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1055"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1056"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1057"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1058"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1059"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="April"/>
+    <n v="1060"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1061"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1062"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1063"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1064"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1065"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1066"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1067"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1068"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1069"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1070"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1071"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1072"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1073"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1074"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1075"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1076"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1077"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="May"/>
+    <n v="1078"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1079"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1080"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1081"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1082"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1083"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1084"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1085"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1086"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1087"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1088"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1089"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1090"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1091"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1092"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1093"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1094"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1095"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1096"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1097"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="June"/>
+    <n v="1098"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1099"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1100"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1101"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1102"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1103"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1104"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <n v="16.3"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1105"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <n v="9.1999999999999993"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1106"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1107"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1108"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1109"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1110"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1111"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1112"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1113"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1114"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1115"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1116"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1117"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1118"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1119"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1120"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1121"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1122"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1123"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="July"/>
+    <n v="1124"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1125"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1126"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1127"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1128"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1129"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1130"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1131"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1132"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1133"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1134"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1135"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1136"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1137"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1138"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1139"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1140"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Aug"/>
+    <n v="1141"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1142"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1143"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1144"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1145"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1146"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1147"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1148"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Sept"/>
+    <n v="1149"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1150"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1151"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1152"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1153"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1154"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1155"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1156"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Oct"/>
+    <n v="1157"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1158"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1159"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1160"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1161"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1162"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1163"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1164"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1165"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <s v="Nov"/>
+    <n v="1166"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <s v="Dec"/>
+    <n v="1167"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <n v="124"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <s v="Dec"/>
+    <n v="1168"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <n v="98.4"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Dec"/>
+    <n v="1169"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <n v="502"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <s v="Dec"/>
+    <n v="1170"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <s v="Dec"/>
+    <n v="1171"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <n v="87"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{268A8983-0403-4910-98F7-0770A3DB0E11}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sale Price" fld="5" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90D4FB98-9A71-4127-A66B-463DBC99FC24}" name="Table1" displayName="Table1" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="1">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K177">
+    <sortCondition ref="B2:B177"/>
+  </sortState>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{57153716-5D83-441C-A0C1-15195763B15B}" name="Month"/>
+    <tableColumn id="2" xr3:uid="{686FDB94-0292-4DC4-AAFE-DF87751C3340}" name="Transaction Number"/>
+    <tableColumn id="3" xr3:uid="{DEEB3688-E0DF-4C43-8424-E9DDF4E9B1E8}" name="Product Code"/>
+    <tableColumn id="4" xr3:uid="{1BCB19DB-AE2F-4ECC-8013-CE3B446EA93D}" name="Product Description"/>
+    <tableColumn id="5" xr3:uid="{E846AF01-8989-4CF8-AFF8-AB66483C2C15}" name="Store Cost"/>
+    <tableColumn id="6" xr3:uid="{453C97C2-0D8F-4ABA-A790-93F6AAF32237}" name="Sale Price"/>
+    <tableColumn id="7" xr3:uid="{CE821A81-7F09-44AA-BA9A-46C121852BD7}" name="Profit"/>
+    <tableColumn id="8" xr3:uid="{BBE3F5D7-4FC0-45AB-98B1-D069C79A4DEC}" name="Commision 10% for items less than 50$. 20% for items more than 50$" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{3A382564-DECE-4349-A6E3-024515D685C5}" name="First Name"/>
+    <tableColumn id="10" xr3:uid="{FD1DA0E6-1D5B-42AE-BE5C-3B66337DEC86}" name="Last Name"/>
+    <tableColumn id="11" xr3:uid="{2043E7E4-8E5A-404F-95A6-C80B6B2E3EEC}" name="Sale Location"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -696,20 +4202,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98733610-7D45-4653-9B5E-324F90078C3D}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6003.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2410.7000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3035.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5">
+        <v>5661.0999999999985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5">
+        <v>17110.599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K172"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" customWidth="1"/>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="78.75">
+    <row r="1" spans="1:11" ht="47.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -731,7 +4303,7 @@
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I1" s="4" t="s">
@@ -767,6 +4339,10 @@
         <f>F2-E2</f>
         <v>40.100000000000009</v>
       </c>
+      <c r="H2" s="3">
+        <f>IF(F2&gt;50, G2*0.2, G2*0.1)</f>
+        <v>8.0200000000000014</v>
+      </c>
       <c r="I2" t="s">
         <v>37</v>
       </c>
@@ -797,8 +4373,12 @@
         <v>16.3</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" ref="G3:G66" si="0">F3-E3</f>
+        <f>F3-E3</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H3" s="7">
+        <f>IF(F3&gt;50, G3*0.2, G3*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
@@ -830,8 +4410,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" si="0"/>
+        <f>F4-E4</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H4" s="3">
+        <f>IF(F4&gt;50, G4*0.2, G4*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I4" t="s">
         <v>41</v>
@@ -863,8 +4447,12 @@
         <v>502</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" si="0"/>
+        <f>F5-E5</f>
         <v>158</v>
+      </c>
+      <c r="H5" s="3">
+        <f>IF(F5&gt;50, G5*0.2, G5*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
@@ -896,8 +4484,12 @@
         <v>8</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" si="0"/>
+        <f>F6-E6</f>
         <v>5</v>
+      </c>
+      <c r="H6" s="3">
+        <f>IF(F6&gt;50, G6*0.2, G6*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I6" t="s">
         <v>41</v>
@@ -929,8 +4521,12 @@
         <v>98.4</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f>F7-E7</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H7" s="3">
+        <f>IF(F7&gt;50, G7*0.2, G7*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I7" t="s">
         <v>41</v>
@@ -962,8 +4558,12 @@
         <v>8</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="0"/>
+        <f>F8-E8</f>
         <v>5</v>
+      </c>
+      <c r="H8" s="3">
+        <f>IF(F8&gt;50, G8*0.2, G8*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
@@ -995,8 +4595,12 @@
         <v>16.3</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="0"/>
+        <f>F9-E9</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H9" s="3">
+        <f>IF(F9&gt;50, G9*0.2, G9*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I9" t="s">
         <v>41</v>
@@ -1028,8 +4632,12 @@
         <v>8</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" si="0"/>
+        <f>F10-E10</f>
         <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <f>IF(F10&gt;50, G10*0.2, G10*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I10" t="s">
         <v>41</v>
@@ -1061,8 +4669,12 @@
         <v>16.3</v>
       </c>
       <c r="G11" s="5">
-        <f t="shared" si="0"/>
+        <f>F11-E11</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H11" s="3">
+        <f>IF(F11&gt;50, G11*0.2, G11*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I11" t="s">
         <v>39</v>
@@ -1094,8 +4706,12 @@
         <v>16.3</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" si="0"/>
+        <f>F12-E12</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H12" s="3">
+        <f>IF(F12&gt;50, G12*0.2, G12*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -1127,8 +4743,12 @@
         <v>87</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="0"/>
+        <f>F13-E13</f>
         <v>42</v>
+      </c>
+      <c r="H13" s="3">
+        <f>IF(F13&gt;50, G13*0.2, G13*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I13" t="s">
         <v>41</v>
@@ -1160,8 +4780,12 @@
         <v>7</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="0"/>
+        <f>F14-E14</f>
         <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <f>IF(F14&gt;50, G14*0.2, G14*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I14" t="s">
         <v>43</v>
@@ -1193,8 +4817,12 @@
         <v>502</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="0"/>
+        <f>F15-E15</f>
         <v>158</v>
+      </c>
+      <c r="H15" s="3">
+        <f>IF(F15&gt;50, G15*0.2, G15*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I15" t="s">
         <v>37</v>
@@ -1226,8 +4854,12 @@
         <v>16.3</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="0"/>
+        <f>F16-E16</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H16" s="3">
+        <f>IF(F16&gt;50, G16*0.2, G16*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I16" t="s">
         <v>43</v>
@@ -1259,8 +4891,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="0"/>
+        <f>F17-E17</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H17" s="3">
+        <f>IF(F17&gt;50, G17*0.2, G17*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I17" t="s">
         <v>41</v>
@@ -1292,8 +4928,12 @@
         <v>124</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="0"/>
+        <f>F18-E18</f>
         <v>64</v>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(F18&gt;50, G18*0.2, G18*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I18" t="s">
         <v>39</v>
@@ -1325,8 +4965,12 @@
         <v>8</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="0"/>
+        <f>F19-E19</f>
         <v>5</v>
+      </c>
+      <c r="H19" s="3">
+        <f>IF(F19&gt;50, G19*0.2, G19*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I19" t="s">
         <v>41</v>
@@ -1358,8 +5002,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="0"/>
+        <f>F20-E20</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H20" s="3">
+        <f>IF(F20&gt;50, G20*0.2, G20*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I20" t="s">
         <v>41</v>
@@ -1391,8 +5039,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="0"/>
+        <f>F21-E21</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H21" s="3">
+        <f>IF(F21&gt;50, G21*0.2, G21*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I21" t="s">
         <v>41</v>
@@ -1424,8 +5076,12 @@
         <v>8</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="0"/>
+        <f>F22-E22</f>
         <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <f>IF(F22&gt;50, G22*0.2, G22*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I22" t="s">
         <v>39</v>
@@ -1457,8 +5113,12 @@
         <v>16.3</v>
       </c>
       <c r="G23" s="5">
-        <f t="shared" si="0"/>
+        <f>F23-E23</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H23" s="3">
+        <f>IF(F23&gt;50, G23*0.2, G23*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
@@ -1490,8 +5150,12 @@
         <v>8</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="0"/>
+        <f>F24-E24</f>
         <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <f>IF(F24&gt;50, G24*0.2, G24*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I24" t="s">
         <v>43</v>
@@ -1523,8 +5187,12 @@
         <v>7</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="0"/>
+        <f>F25-E25</f>
         <v>3</v>
+      </c>
+      <c r="H25" s="3">
+        <f>IF(F25&gt;50, G25*0.2, G25*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I25" t="s">
         <v>39</v>
@@ -1556,8 +5224,12 @@
         <v>16.3</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="0"/>
+        <f>F26-E26</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H26" s="3">
+        <f>IF(F26&gt;50, G26*0.2, G26*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I26" t="s">
         <v>43</v>
@@ -1589,8 +5261,12 @@
         <v>14</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="0"/>
+        <f>F27-E27</f>
         <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <f>IF(F27&gt;50, G27*0.2, G27*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I27" t="s">
         <v>43</v>
@@ -1622,8 +5298,12 @@
         <v>14</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="0"/>
+        <f>F28-E28</f>
         <v>5</v>
+      </c>
+      <c r="H28" s="3">
+        <f>IF(F28&gt;50, G28*0.2, G28*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I28" t="s">
         <v>37</v>
@@ -1655,8 +5335,12 @@
         <v>502</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" si="0"/>
+        <f>F29-E29</f>
         <v>158</v>
+      </c>
+      <c r="H29" s="3">
+        <f>IF(F29&gt;50, G29*0.2, G29*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I29" t="s">
         <v>37</v>
@@ -1688,8 +5372,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G30" s="5">
-        <f t="shared" si="0"/>
+        <f>F30-E30</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H30" s="3">
+        <f>IF(F30&gt;50, G30*0.2, G30*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I30" t="s">
         <v>39</v>
@@ -1721,8 +5409,12 @@
         <v>87</v>
       </c>
       <c r="G31" s="5">
-        <f t="shared" si="0"/>
+        <f>F31-E31</f>
         <v>42</v>
+      </c>
+      <c r="H31" s="3">
+        <f>IF(F31&gt;50, G31*0.2, G31*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I31" t="s">
         <v>39</v>
@@ -1754,8 +5446,12 @@
         <v>8</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" si="0"/>
+        <f>F32-E32</f>
         <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <f>IF(F32&gt;50, G32*0.2, G32*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I32" t="s">
         <v>39</v>
@@ -1787,8 +5483,12 @@
         <v>16.3</v>
       </c>
       <c r="G33" s="5">
-        <f t="shared" si="0"/>
+        <f>F33-E33</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H33" s="3">
+        <f>IF(F33&gt;50, G33*0.2, G33*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I33" t="s">
         <v>37</v>
@@ -1820,8 +5520,12 @@
         <v>98.4</v>
       </c>
       <c r="G34" s="5">
-        <f t="shared" si="0"/>
+        <f>F34-E34</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H34" s="3">
+        <f>IF(F34&gt;50, G34*0.2, G34*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I34" t="s">
         <v>39</v>
@@ -1853,8 +5557,12 @@
         <v>16.3</v>
       </c>
       <c r="G35" s="5">
-        <f t="shared" si="0"/>
+        <f>F35-E35</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H35" s="3">
+        <f>IF(F35&gt;50, G35*0.2, G35*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I35" t="s">
         <v>39</v>
@@ -1886,8 +5594,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G36" s="5">
-        <f t="shared" si="0"/>
+        <f>F36-E36</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H36" s="3">
+        <f>IF(F36&gt;50, G36*0.2, G36*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I36" t="s">
         <v>43</v>
@@ -1919,8 +5631,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G37" s="5">
-        <f t="shared" si="0"/>
+        <f>F37-E37</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H37" s="3">
+        <f>IF(F37&gt;50, G37*0.2, G37*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I37" t="s">
         <v>39</v>
@@ -1952,8 +5668,12 @@
         <v>77</v>
       </c>
       <c r="G38" s="5">
-        <f t="shared" si="0"/>
+        <f>F38-E38</f>
         <v>35</v>
+      </c>
+      <c r="H38" s="3">
+        <f>IF(F38&gt;50, G38*0.2, G38*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I38" t="s">
         <v>39</v>
@@ -1985,8 +5705,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" si="0"/>
+        <f>F39-E39</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H39" s="3">
+        <f>IF(F39&gt;50, G39*0.2, G39*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I39" t="s">
         <v>39</v>
@@ -2018,8 +5742,12 @@
         <v>16.3</v>
       </c>
       <c r="G40" s="5">
-        <f t="shared" si="0"/>
+        <f>F40-E40</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H40" s="3">
+        <f>IF(F40&gt;50, G40*0.2, G40*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I40" t="s">
         <v>39</v>
@@ -2051,8 +5779,12 @@
         <v>8</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" si="0"/>
+        <f>F41-E41</f>
         <v>5</v>
+      </c>
+      <c r="H41" s="3">
+        <f>IF(F41&gt;50, G41*0.2, G41*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I41" t="s">
         <v>39</v>
@@ -2084,8 +5816,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" si="0"/>
+        <f>F42-E42</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H42" s="3">
+        <f>IF(F42&gt;50, G42*0.2, G42*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I42" t="s">
         <v>37</v>
@@ -2117,8 +5853,12 @@
         <v>502</v>
       </c>
       <c r="G43" s="5">
-        <f t="shared" si="0"/>
+        <f>F43-E43</f>
         <v>158</v>
+      </c>
+      <c r="H43" s="3">
+        <f>IF(F43&gt;50, G43*0.2, G43*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I43" t="s">
         <v>41</v>
@@ -2150,8 +5890,12 @@
         <v>124</v>
       </c>
       <c r="G44" s="5">
-        <f t="shared" si="0"/>
+        <f>F44-E44</f>
         <v>64</v>
+      </c>
+      <c r="H44" s="3">
+        <f>IF(F44&gt;50, G44*0.2, G44*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I44" t="s">
         <v>41</v>
@@ -2183,8 +5927,12 @@
         <v>16.3</v>
       </c>
       <c r="G45" s="5">
-        <f t="shared" si="0"/>
+        <f>F45-E45</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H45" s="3">
+        <f>IF(F45&gt;50, G45*0.2, G45*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I45" t="s">
         <v>41</v>
@@ -2216,8 +5964,12 @@
         <v>502</v>
       </c>
       <c r="G46" s="5">
-        <f t="shared" si="0"/>
+        <f>F46-E46</f>
         <v>158</v>
+      </c>
+      <c r="H46" s="3">
+        <f>IF(F46&gt;50, G46*0.2, G46*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I46" t="s">
         <v>43</v>
@@ -2249,8 +6001,12 @@
         <v>14</v>
       </c>
       <c r="G47" s="5">
-        <f t="shared" si="0"/>
+        <f>F47-E47</f>
         <v>5</v>
+      </c>
+      <c r="H47" s="3">
+        <f>IF(F47&gt;50, G47*0.2, G47*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I47" t="s">
         <v>39</v>
@@ -2282,8 +6038,12 @@
         <v>77</v>
       </c>
       <c r="G48" s="5">
-        <f t="shared" si="0"/>
+        <f>F48-E48</f>
         <v>35</v>
+      </c>
+      <c r="H48" s="3">
+        <f>IF(F48&gt;50, G48*0.2, G48*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I48" t="s">
         <v>43</v>
@@ -2315,8 +6075,12 @@
         <v>502</v>
       </c>
       <c r="G49" s="5">
-        <f t="shared" si="0"/>
+        <f>F49-E49</f>
         <v>158</v>
+      </c>
+      <c r="H49" s="3">
+        <f>IF(F49&gt;50, G49*0.2, G49*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I49" t="s">
         <v>37</v>
@@ -2348,8 +6112,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G50" s="5">
-        <f t="shared" si="0"/>
+        <f>F50-E50</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H50" s="3">
+        <f>IF(F50&gt;50, G50*0.2, G50*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I50" t="s">
         <v>37</v>
@@ -2381,8 +6149,12 @@
         <v>16.3</v>
       </c>
       <c r="G51" s="5">
-        <f t="shared" si="0"/>
+        <f>F51-E51</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H51" s="3">
+        <f>IF(F51&gt;50, G51*0.2, G51*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I51" t="s">
         <v>37</v>
@@ -2414,8 +6186,12 @@
         <v>14</v>
       </c>
       <c r="G52" s="5">
-        <f t="shared" si="0"/>
+        <f>F52-E52</f>
         <v>5</v>
+      </c>
+      <c r="H52" s="3">
+        <f>IF(F52&gt;50, G52*0.2, G52*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I52" t="s">
         <v>41</v>
@@ -2447,8 +6223,12 @@
         <v>77</v>
       </c>
       <c r="G53" s="5">
-        <f t="shared" si="0"/>
+        <f>F53-E53</f>
         <v>35</v>
+      </c>
+      <c r="H53" s="3">
+        <f>IF(F53&gt;50, G53*0.2, G53*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I53" t="s">
         <v>41</v>
@@ -2480,8 +6260,12 @@
         <v>124</v>
       </c>
       <c r="G54" s="5">
-        <f t="shared" si="0"/>
+        <f>F54-E54</f>
         <v>64</v>
+      </c>
+      <c r="H54" s="3">
+        <f>IF(F54&gt;50, G54*0.2, G54*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I54" t="s">
         <v>37</v>
@@ -2513,8 +6297,12 @@
         <v>87</v>
       </c>
       <c r="G55" s="5">
-        <f t="shared" si="0"/>
+        <f>F55-E55</f>
         <v>42</v>
+      </c>
+      <c r="H55" s="3">
+        <f>IF(F55&gt;50, G55*0.2, G55*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I55" t="s">
         <v>41</v>
@@ -2546,8 +6334,12 @@
         <v>14</v>
       </c>
       <c r="G56" s="5">
-        <f t="shared" si="0"/>
+        <f>F56-E56</f>
         <v>5</v>
+      </c>
+      <c r="H56" s="3">
+        <f>IF(F56&gt;50, G56*0.2, G56*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I56" t="s">
         <v>39</v>
@@ -2579,8 +6371,12 @@
         <v>8</v>
       </c>
       <c r="G57" s="5">
-        <f t="shared" si="0"/>
+        <f>F57-E57</f>
         <v>5</v>
+      </c>
+      <c r="H57" s="3">
+        <f>IF(F57&gt;50, G57*0.2, G57*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I57" t="s">
         <v>41</v>
@@ -2612,8 +6408,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G58" s="5">
-        <f t="shared" si="0"/>
+        <f>F58-E58</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H58" s="3">
+        <f>IF(F58&gt;50, G58*0.2, G58*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I58" t="s">
         <v>39</v>
@@ -2645,8 +6445,12 @@
         <v>14</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="0"/>
+        <f>F59-E59</f>
         <v>5</v>
+      </c>
+      <c r="H59" s="3">
+        <f>IF(F59&gt;50, G59*0.2, G59*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I59" t="s">
         <v>43</v>
@@ -2678,8 +6482,12 @@
         <v>124</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" si="0"/>
+        <f>F60-E60</f>
         <v>64</v>
+      </c>
+      <c r="H60" s="3">
+        <f>IF(F60&gt;50, G60*0.2, G60*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I60" t="s">
         <v>41</v>
@@ -2711,8 +6519,12 @@
         <v>14</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="0"/>
+        <f>F61-E61</f>
         <v>5</v>
+      </c>
+      <c r="H61" s="3">
+        <f>IF(F61&gt;50, G61*0.2, G61*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I61" t="s">
         <v>41</v>
@@ -2744,8 +6556,12 @@
         <v>8</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="0"/>
+        <f>F62-E62</f>
         <v>5</v>
+      </c>
+      <c r="H62" s="3">
+        <f>IF(F62&gt;50, G62*0.2, G62*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I62" t="s">
         <v>41</v>
@@ -2777,8 +6593,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G63" s="5">
-        <f t="shared" si="0"/>
+        <f>F63-E63</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H63" s="3">
+        <f>IF(F63&gt;50, G63*0.2, G63*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I63" t="s">
         <v>37</v>
@@ -2810,8 +6630,12 @@
         <v>8</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="0"/>
+        <f>F64-E64</f>
         <v>5</v>
+      </c>
+      <c r="H64" s="3">
+        <f>IF(F64&gt;50, G64*0.2, G64*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I64" t="s">
         <v>41</v>
@@ -2843,8 +6667,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G65" s="5">
-        <f t="shared" si="0"/>
+        <f>F65-E65</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H65" s="3">
+        <f>IF(F65&gt;50, G65*0.2, G65*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I65" t="s">
         <v>43</v>
@@ -2876,8 +6704,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G66" s="5">
-        <f t="shared" si="0"/>
+        <f>F66-E66</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H66" s="3">
+        <f>IF(F66&gt;50, G66*0.2, G66*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I66" t="s">
         <v>41</v>
@@ -2909,8 +6741,12 @@
         <v>16.3</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" ref="G67:G130" si="1">F67-E67</f>
+        <f>F67-E67</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H67" s="3">
+        <f>IF(F67&gt;50, G67*0.2, G67*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I67" t="s">
         <v>41</v>
@@ -2942,8 +6778,12 @@
         <v>16.3</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" si="1"/>
+        <f>F68-E68</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H68" s="3">
+        <f>IF(F68&gt;50, G68*0.2, G68*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I68" t="s">
         <v>41</v>
@@ -2975,8 +6815,12 @@
         <v>14</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="1"/>
+        <f>F69-E69</f>
         <v>5</v>
+      </c>
+      <c r="H69" s="3">
+        <f>IF(F69&gt;50, G69*0.2, G69*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I69" t="s">
         <v>39</v>
@@ -3008,8 +6852,12 @@
         <v>8</v>
       </c>
       <c r="G70" s="5">
-        <f t="shared" si="1"/>
+        <f>F70-E70</f>
         <v>5</v>
+      </c>
+      <c r="H70" s="3">
+        <f>IF(F70&gt;50, G70*0.2, G70*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I70" t="s">
         <v>41</v>
@@ -3041,8 +6889,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G71" s="5">
-        <f t="shared" si="1"/>
+        <f>F71-E71</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H71" s="3">
+        <f>IF(F71&gt;50, G71*0.2, G71*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I71" t="s">
         <v>43</v>
@@ -3074,8 +6926,12 @@
         <v>8</v>
       </c>
       <c r="G72" s="5">
-        <f t="shared" si="1"/>
+        <f>F72-E72</f>
         <v>5</v>
+      </c>
+      <c r="H72" s="3">
+        <f>IF(F72&gt;50, G72*0.2, G72*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I72" t="s">
         <v>37</v>
@@ -3107,8 +6963,12 @@
         <v>8</v>
       </c>
       <c r="G73" s="5">
-        <f t="shared" si="1"/>
+        <f>F73-E73</f>
         <v>5</v>
+      </c>
+      <c r="H73" s="3">
+        <f>IF(F73&gt;50, G73*0.2, G73*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I73" t="s">
         <v>41</v>
@@ -3140,8 +7000,12 @@
         <v>77</v>
       </c>
       <c r="G74" s="5">
-        <f t="shared" si="1"/>
+        <f>F74-E74</f>
         <v>35</v>
+      </c>
+      <c r="H74" s="3">
+        <f>IF(F74&gt;50, G74*0.2, G74*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I74" t="s">
         <v>41</v>
@@ -3173,8 +7037,12 @@
         <v>16.3</v>
       </c>
       <c r="G75" s="5">
-        <f t="shared" si="1"/>
+        <f>F75-E75</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H75" s="3">
+        <f>IF(F75&gt;50, G75*0.2, G75*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I75" t="s">
         <v>41</v>
@@ -3206,8 +7074,12 @@
         <v>8</v>
       </c>
       <c r="G76" s="5">
-        <f t="shared" si="1"/>
+        <f>F76-E76</f>
         <v>5</v>
+      </c>
+      <c r="H76" s="3">
+        <f>IF(F76&gt;50, G76*0.2, G76*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I76" t="s">
         <v>43</v>
@@ -3239,8 +7111,12 @@
         <v>8</v>
       </c>
       <c r="G77" s="5">
-        <f t="shared" si="1"/>
+        <f>F77-E77</f>
         <v>5</v>
+      </c>
+      <c r="H77" s="3">
+        <f>IF(F77&gt;50, G77*0.2, G77*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I77" t="s">
         <v>39</v>
@@ -3272,8 +7148,12 @@
         <v>98.4</v>
       </c>
       <c r="G78" s="5">
-        <f t="shared" si="1"/>
+        <f>F78-E78</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H78" s="3">
+        <f>IF(F78&gt;50, G78*0.2, G78*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I78" t="s">
         <v>43</v>
@@ -3305,8 +7185,12 @@
         <v>16.3</v>
       </c>
       <c r="G79" s="5">
-        <f t="shared" si="1"/>
+        <f>F79-E79</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H79" s="3">
+        <f>IF(F79&gt;50, G79*0.2, G79*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I79" t="s">
         <v>39</v>
@@ -3338,8 +7222,12 @@
         <v>16.3</v>
       </c>
       <c r="G80" s="5">
-        <f t="shared" si="1"/>
+        <f>F80-E80</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H80" s="3">
+        <f>IF(F80&gt;50, G80*0.2, G80*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I80" t="s">
         <v>39</v>
@@ -3371,8 +7259,12 @@
         <v>87</v>
       </c>
       <c r="G81" s="5">
-        <f t="shared" si="1"/>
+        <f>F81-E81</f>
         <v>42</v>
+      </c>
+      <c r="H81" s="3">
+        <f>IF(F81&gt;50, G81*0.2, G81*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I81" t="s">
         <v>41</v>
@@ -3404,8 +7296,12 @@
         <v>14</v>
       </c>
       <c r="G82" s="5">
-        <f t="shared" si="1"/>
+        <f>F82-E82</f>
         <v>5</v>
+      </c>
+      <c r="H82" s="3">
+        <f>IF(F82&gt;50, G82*0.2, G82*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I82" t="s">
         <v>41</v>
@@ -3437,8 +7333,12 @@
         <v>8</v>
       </c>
       <c r="G83" s="5">
-        <f t="shared" si="1"/>
+        <f>F83-E83</f>
         <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <f>IF(F83&gt;50, G83*0.2, G83*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I83" t="s">
         <v>37</v>
@@ -3470,8 +7370,12 @@
         <v>8</v>
       </c>
       <c r="G84" s="5">
-        <f t="shared" si="1"/>
+        <f>F84-E84</f>
         <v>5</v>
+      </c>
+      <c r="H84" s="3">
+        <f>IF(F84&gt;50, G84*0.2, G84*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I84" t="s">
         <v>37</v>
@@ -3503,8 +7407,12 @@
         <v>14</v>
       </c>
       <c r="G85" s="5">
-        <f t="shared" si="1"/>
+        <f>F85-E85</f>
         <v>5</v>
+      </c>
+      <c r="H85" s="3">
+        <f>IF(F85&gt;50, G85*0.2, G85*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I85" t="s">
         <v>37</v>
@@ -3536,8 +7444,12 @@
         <v>98.4</v>
       </c>
       <c r="G86" s="5">
-        <f t="shared" si="1"/>
+        <f>F86-E86</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H86" s="3">
+        <f>IF(F86&gt;50, G86*0.2, G86*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I86" t="s">
         <v>41</v>
@@ -3569,8 +7481,12 @@
         <v>8</v>
       </c>
       <c r="G87" s="5">
-        <f t="shared" si="1"/>
+        <f>F87-E87</f>
         <v>5</v>
+      </c>
+      <c r="H87" s="3">
+        <f>IF(F87&gt;50, G87*0.2, G87*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I87" t="s">
         <v>43</v>
@@ -3602,8 +7518,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G88" s="5">
-        <f t="shared" si="1"/>
+        <f>F88-E88</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H88" s="3">
+        <f>IF(F88&gt;50, G88*0.2, G88*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I88" t="s">
         <v>37</v>
@@ -3635,8 +7555,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G89" s="5">
-        <f t="shared" si="1"/>
+        <f>F89-E89</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H89" s="3">
+        <f>IF(F89&gt;50, G89*0.2, G89*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I89" t="s">
         <v>37</v>
@@ -3668,8 +7592,12 @@
         <v>14</v>
       </c>
       <c r="G90" s="5">
-        <f t="shared" si="1"/>
+        <f>F90-E90</f>
         <v>5</v>
+      </c>
+      <c r="H90" s="3">
+        <f>IF(F90&gt;50, G90*0.2, G90*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I90" t="s">
         <v>41</v>
@@ -3701,8 +7629,12 @@
         <v>16.3</v>
       </c>
       <c r="G91" s="5">
-        <f t="shared" si="1"/>
+        <f>F91-E91</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H91" s="3">
+        <f>IF(F91&gt;50, G91*0.2, G91*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I91" t="s">
         <v>37</v>
@@ -3734,8 +7666,12 @@
         <v>16.3</v>
       </c>
       <c r="G92" s="5">
-        <f t="shared" si="1"/>
+        <f>F92-E92</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H92" s="3">
+        <f>IF(F92&gt;50, G92*0.2, G92*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I92" t="s">
         <v>43</v>
@@ -3767,8 +7703,12 @@
         <v>16.3</v>
       </c>
       <c r="G93" s="5">
-        <f t="shared" si="1"/>
+        <f>F93-E93</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H93" s="3">
+        <f>IF(F93&gt;50, G93*0.2, G93*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I93" t="s">
         <v>41</v>
@@ -3800,8 +7740,12 @@
         <v>14</v>
       </c>
       <c r="G94" s="5">
-        <f t="shared" si="1"/>
+        <f>F94-E94</f>
         <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <f>IF(F94&gt;50, G94*0.2, G94*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I94" t="s">
         <v>39</v>
@@ -3833,8 +7777,12 @@
         <v>14</v>
       </c>
       <c r="G95" s="5">
-        <f t="shared" si="1"/>
+        <f>F95-E95</f>
         <v>5</v>
+      </c>
+      <c r="H95" s="3">
+        <f>IF(F95&gt;50, G95*0.2, G95*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I95" t="s">
         <v>41</v>
@@ -3866,8 +7814,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G96" s="5">
-        <f t="shared" si="1"/>
+        <f>F96-E96</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H96" s="3">
+        <f>IF(F96&gt;50, G96*0.2, G96*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I96" t="s">
         <v>43</v>
@@ -3899,8 +7851,12 @@
         <v>14</v>
       </c>
       <c r="G97" s="5">
-        <f t="shared" si="1"/>
+        <f>F97-E97</f>
         <v>5</v>
+      </c>
+      <c r="H97" s="3">
+        <f>IF(F97&gt;50, G97*0.2, G97*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I97" t="s">
         <v>41</v>
@@ -3932,8 +7888,12 @@
         <v>7</v>
       </c>
       <c r="G98" s="5">
-        <f t="shared" si="1"/>
+        <f>F98-E98</f>
         <v>3</v>
+      </c>
+      <c r="H98" s="3">
+        <f>IF(F98&gt;50, G98*0.2, G98*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I98" t="s">
         <v>43</v>
@@ -3965,8 +7925,12 @@
         <v>16.3</v>
       </c>
       <c r="G99" s="5">
-        <f t="shared" si="1"/>
+        <f>F99-E99</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H99" s="3">
+        <f>IF(F99&gt;50, G99*0.2, G99*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I99" t="s">
         <v>39</v>
@@ -3998,8 +7962,12 @@
         <v>16.3</v>
       </c>
       <c r="G100" s="5">
-        <f t="shared" si="1"/>
+        <f>F100-E100</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H100" s="3">
+        <f>IF(F100&gt;50, G100*0.2, G100*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I100" t="s">
         <v>41</v>
@@ -4031,8 +7999,12 @@
         <v>14</v>
       </c>
       <c r="G101" s="5">
-        <f t="shared" si="1"/>
+        <f>F101-E101</f>
         <v>5</v>
+      </c>
+      <c r="H101" s="3">
+        <f>IF(F101&gt;50, G101*0.2, G101*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I101" t="s">
         <v>37</v>
@@ -4064,8 +8036,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G102" s="5">
-        <f t="shared" si="1"/>
+        <f>F102-E102</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H102" s="3">
+        <f>IF(F102&gt;50, G102*0.2, G102*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I102" t="s">
         <v>41</v>
@@ -4097,8 +8073,12 @@
         <v>124</v>
       </c>
       <c r="G103" s="5">
-        <f t="shared" si="1"/>
+        <f>F103-E103</f>
         <v>64</v>
+      </c>
+      <c r="H103" s="3">
+        <f>IF(F103&gt;50, G103*0.2, G103*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I103" t="s">
         <v>39</v>
@@ -4130,8 +8110,12 @@
         <v>16.3</v>
       </c>
       <c r="G104" s="5">
-        <f t="shared" si="1"/>
+        <f>F104-E104</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H104" s="3">
+        <f>IF(F104&gt;50, G104*0.2, G104*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I104" t="s">
         <v>39</v>
@@ -4163,8 +8147,12 @@
         <v>16.3</v>
       </c>
       <c r="G105" s="5">
-        <f t="shared" si="1"/>
+        <f>F105-E105</f>
         <v>4.9000000000000004</v>
+      </c>
+      <c r="H105" s="3">
+        <f>IF(F105&gt;50, G105*0.2, G105*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I105" t="s">
         <v>41</v>
@@ -4196,8 +8184,12 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G106" s="5">
-        <f t="shared" si="1"/>
+        <f>F106-E106</f>
         <v>2.9999999999999991</v>
+      </c>
+      <c r="H106" s="3">
+        <f>IF(F106&gt;50, G106*0.2, G106*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I106" t="s">
         <v>39</v>
@@ -4229,8 +8221,12 @@
         <v>98.4</v>
       </c>
       <c r="G107" s="5">
-        <f t="shared" si="1"/>
+        <f>F107-E107</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H107" s="3">
+        <f>IF(F107&gt;50, G107*0.2, G107*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I107" t="s">
         <v>39</v>
@@ -4262,8 +8258,12 @@
         <v>8</v>
       </c>
       <c r="G108" s="5">
-        <f t="shared" si="1"/>
+        <f>F108-E108</f>
         <v>5</v>
+      </c>
+      <c r="H108" s="3">
+        <f>IF(F108&gt;50, G108*0.2, G108*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I108" t="s">
         <v>43</v>
@@ -4295,8 +8295,12 @@
         <v>98.4</v>
       </c>
       <c r="G109" s="5">
-        <f t="shared" si="1"/>
+        <f>F109-E109</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H109" s="3">
+        <f>IF(F109&gt;50, G109*0.2, G109*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I109" t="s">
         <v>41</v>
@@ -4328,8 +8332,12 @@
         <v>502</v>
       </c>
       <c r="G110" s="5">
-        <f t="shared" si="1"/>
+        <f>F110-E110</f>
         <v>158</v>
+      </c>
+      <c r="H110" s="3">
+        <f>IF(F110&gt;50, G110*0.2, G110*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I110" t="s">
         <v>39</v>
@@ -4361,8 +8369,12 @@
         <v>502</v>
       </c>
       <c r="G111" s="5">
-        <f t="shared" si="1"/>
+        <f>F111-E111</f>
         <v>158</v>
+      </c>
+      <c r="H111" s="3">
+        <f>IF(F111&gt;50, G111*0.2, G111*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I111" t="s">
         <v>43</v>
@@ -4394,8 +8406,12 @@
         <v>77</v>
       </c>
       <c r="G112" s="5">
-        <f t="shared" si="1"/>
+        <f>F112-E112</f>
         <v>35</v>
+      </c>
+      <c r="H112" s="3">
+        <f>IF(F112&gt;50, G112*0.2, G112*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I112" t="s">
         <v>43</v>
@@ -4427,8 +8443,12 @@
         <v>77</v>
       </c>
       <c r="G113" s="5">
-        <f t="shared" si="1"/>
+        <f>F113-E113</f>
         <v>35</v>
+      </c>
+      <c r="H113" s="3">
+        <f>IF(F113&gt;50, G113*0.2, G113*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I113" t="s">
         <v>41</v>
@@ -4460,8 +8480,12 @@
         <v>98.4</v>
       </c>
       <c r="G114" s="5">
-        <f t="shared" si="1"/>
+        <f>F114-E114</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H114" s="3">
+        <f>IF(F114&gt;50, G114*0.2, G114*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I114" t="s">
         <v>37</v>
@@ -4493,8 +8517,12 @@
         <v>124</v>
       </c>
       <c r="G115" s="5">
-        <f t="shared" si="1"/>
+        <f>F115-E115</f>
         <v>64</v>
+      </c>
+      <c r="H115" s="3">
+        <f>IF(F115&gt;50, G115*0.2, G115*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I115" t="s">
         <v>39</v>
@@ -4526,8 +8554,12 @@
         <v>502</v>
       </c>
       <c r="G116" s="5">
-        <f t="shared" si="1"/>
+        <f>F116-E116</f>
         <v>158</v>
+      </c>
+      <c r="H116" s="3">
+        <f>IF(F116&gt;50, G116*0.2, G116*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I116" t="s">
         <v>37</v>
@@ -4559,8 +8591,12 @@
         <v>77</v>
       </c>
       <c r="G117" s="5">
-        <f t="shared" si="1"/>
+        <f>F117-E117</f>
         <v>35</v>
+      </c>
+      <c r="H117" s="3">
+        <f>IF(F117&gt;50, G117*0.2, G117*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I117" t="s">
         <v>41</v>
@@ -4592,8 +8628,12 @@
         <v>502</v>
       </c>
       <c r="G118" s="5">
-        <f t="shared" si="1"/>
+        <f>F118-E118</f>
         <v>158</v>
+      </c>
+      <c r="H118" s="3">
+        <f>IF(F118&gt;50, G118*0.2, G118*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I118" t="s">
         <v>43</v>
@@ -4625,8 +8665,12 @@
         <v>98.4</v>
       </c>
       <c r="G119" s="5">
-        <f t="shared" si="1"/>
+        <f>F119-E119</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H119" s="3">
+        <f>IF(F119&gt;50, G119*0.2, G119*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I119" t="s">
         <v>39</v>
@@ -4658,8 +8702,12 @@
         <v>124</v>
       </c>
       <c r="G120" s="5">
-        <f t="shared" si="1"/>
+        <f>F120-E120</f>
         <v>64</v>
+      </c>
+      <c r="H120" s="3">
+        <f>IF(F120&gt;50, G120*0.2, G120*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I120" t="s">
         <v>37</v>
@@ -4691,8 +8739,12 @@
         <v>124</v>
       </c>
       <c r="G121" s="5">
-        <f t="shared" si="1"/>
+        <f>F121-E121</f>
         <v>64</v>
+      </c>
+      <c r="H121" s="3">
+        <f>IF(F121&gt;50, G121*0.2, G121*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I121" t="s">
         <v>41</v>
@@ -4724,8 +8776,12 @@
         <v>87</v>
       </c>
       <c r="G122" s="5">
-        <f t="shared" si="1"/>
+        <f>F122-E122</f>
         <v>42</v>
+      </c>
+      <c r="H122" s="3">
+        <f>IF(F122&gt;50, G122*0.2, G122*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I122" t="s">
         <v>41</v>
@@ -4757,8 +8813,12 @@
         <v>502</v>
       </c>
       <c r="G123" s="5">
-        <f t="shared" si="1"/>
+        <f>F123-E123</f>
         <v>158</v>
+      </c>
+      <c r="H123" s="3">
+        <f>IF(F123&gt;50, G123*0.2, G123*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I123" t="s">
         <v>41</v>
@@ -4790,8 +8850,12 @@
         <v>98.4</v>
       </c>
       <c r="G124" s="5">
-        <f t="shared" si="1"/>
+        <f>F124-E124</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H124" s="3">
+        <f>IF(F124&gt;50, G124*0.2, G124*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I124" t="s">
         <v>41</v>
@@ -4823,8 +8887,12 @@
         <v>87</v>
       </c>
       <c r="G125" s="5">
-        <f t="shared" si="1"/>
+        <f>F125-E125</f>
         <v>42</v>
+      </c>
+      <c r="H125" s="3">
+        <f>IF(F125&gt;50, G125*0.2, G125*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I125" t="s">
         <v>41</v>
@@ -4856,8 +8924,12 @@
         <v>124</v>
       </c>
       <c r="G126" s="5">
-        <f t="shared" si="1"/>
+        <f>F126-E126</f>
         <v>64</v>
+      </c>
+      <c r="H126" s="3">
+        <f>IF(F126&gt;50, G126*0.2, G126*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I126" t="s">
         <v>41</v>
@@ -4889,8 +8961,12 @@
         <v>7</v>
       </c>
       <c r="G127" s="5">
-        <f t="shared" si="1"/>
+        <f>F127-E127</f>
         <v>3</v>
+      </c>
+      <c r="H127" s="3">
+        <f>IF(F127&gt;50, G127*0.2, G127*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I127" t="s">
         <v>41</v>
@@ -4922,8 +8998,12 @@
         <v>502</v>
       </c>
       <c r="G128" s="5">
-        <f t="shared" si="1"/>
+        <f>F128-E128</f>
         <v>158</v>
+      </c>
+      <c r="H128" s="3">
+        <f>IF(F128&gt;50, G128*0.2, G128*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I128" t="s">
         <v>37</v>
@@ -4955,8 +9035,12 @@
         <v>77</v>
       </c>
       <c r="G129" s="5">
-        <f t="shared" si="1"/>
+        <f>F129-E129</f>
         <v>35</v>
+      </c>
+      <c r="H129" s="3">
+        <f>IF(F129&gt;50, G129*0.2, G129*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I129" t="s">
         <v>39</v>
@@ -4988,8 +9072,12 @@
         <v>98.4</v>
       </c>
       <c r="G130" s="5">
-        <f t="shared" si="1"/>
+        <f>F130-E130</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H130" s="3">
+        <f>IF(F130&gt;50, G130*0.2, G130*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I130" t="s">
         <v>43</v>
@@ -5021,8 +9109,12 @@
         <v>87</v>
       </c>
       <c r="G131" s="5">
-        <f t="shared" ref="G131:G172" si="2">F131-E131</f>
+        <f>F131-E131</f>
         <v>42</v>
+      </c>
+      <c r="H131" s="3">
+        <f>IF(F131&gt;50, G131*0.2, G131*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I131" t="s">
         <v>43</v>
@@ -5054,8 +9146,12 @@
         <v>7</v>
       </c>
       <c r="G132" s="5">
-        <f t="shared" si="2"/>
+        <f>F132-E132</f>
         <v>3</v>
+      </c>
+      <c r="H132" s="3">
+        <f>IF(F132&gt;50, G132*0.2, G132*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I132" t="s">
         <v>43</v>
@@ -5087,8 +9183,12 @@
         <v>7</v>
       </c>
       <c r="G133" s="5">
-        <f t="shared" si="2"/>
+        <f>F133-E133</f>
         <v>3</v>
+      </c>
+      <c r="H133" s="3">
+        <f>IF(F133&gt;50, G133*0.2, G133*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I133" t="s">
         <v>43</v>
@@ -5120,8 +9220,12 @@
         <v>98.4</v>
       </c>
       <c r="G134" s="5">
-        <f t="shared" si="2"/>
+        <f>F134-E134</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H134" s="3">
+        <f>IF(F134&gt;50, G134*0.2, G134*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I134" t="s">
         <v>37</v>
@@ -5153,8 +9257,12 @@
         <v>98.4</v>
       </c>
       <c r="G135" s="5">
-        <f t="shared" si="2"/>
+        <f>F135-E135</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H135" s="3">
+        <f>IF(F135&gt;50, G135*0.2, G135*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I135" t="s">
         <v>41</v>
@@ -5186,8 +9294,12 @@
         <v>502</v>
       </c>
       <c r="G136" s="5">
-        <f t="shared" si="2"/>
+        <f>F136-E136</f>
         <v>158</v>
+      </c>
+      <c r="H136" s="3">
+        <f>IF(F136&gt;50, G136*0.2, G136*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I136" t="s">
         <v>37</v>
@@ -5219,8 +9331,12 @@
         <v>124</v>
       </c>
       <c r="G137" s="5">
-        <f t="shared" si="2"/>
+        <f>F137-E137</f>
         <v>64</v>
+      </c>
+      <c r="H137" s="3">
+        <f>IF(F137&gt;50, G137*0.2, G137*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I137" t="s">
         <v>41</v>
@@ -5252,8 +9368,12 @@
         <v>98.4</v>
       </c>
       <c r="G138" s="5">
-        <f t="shared" si="2"/>
+        <f>F138-E138</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H138" s="3">
+        <f>IF(F138&gt;50, G138*0.2, G138*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I138" t="s">
         <v>39</v>
@@ -5285,8 +9405,12 @@
         <v>502</v>
       </c>
       <c r="G139" s="5">
-        <f t="shared" si="2"/>
+        <f>F139-E139</f>
         <v>158</v>
+      </c>
+      <c r="H139" s="3">
+        <f>IF(F139&gt;50, G139*0.2, G139*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I139" t="s">
         <v>37</v>
@@ -5318,8 +9442,12 @@
         <v>87</v>
       </c>
       <c r="G140" s="5">
-        <f t="shared" si="2"/>
+        <f>F140-E140</f>
         <v>42</v>
+      </c>
+      <c r="H140" s="3">
+        <f>IF(F140&gt;50, G140*0.2, G140*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I140" t="s">
         <v>41</v>
@@ -5351,8 +9479,12 @@
         <v>87</v>
       </c>
       <c r="G141" s="5">
-        <f t="shared" si="2"/>
+        <f>F141-E141</f>
         <v>42</v>
+      </c>
+      <c r="H141" s="3">
+        <f>IF(F141&gt;50, G141*0.2, G141*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I141" t="s">
         <v>39</v>
@@ -5384,8 +9516,12 @@
         <v>7</v>
       </c>
       <c r="G142" s="5">
-        <f t="shared" si="2"/>
+        <f>F142-E142</f>
         <v>3</v>
+      </c>
+      <c r="H142" s="3">
+        <f>IF(F142&gt;50, G142*0.2, G142*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I142" t="s">
         <v>39</v>
@@ -5417,8 +9553,12 @@
         <v>124</v>
       </c>
       <c r="G143" s="5">
-        <f t="shared" si="2"/>
+        <f>F143-E143</f>
         <v>64</v>
+      </c>
+      <c r="H143" s="3">
+        <f>IF(F143&gt;50, G143*0.2, G143*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I143" t="s">
         <v>39</v>
@@ -5450,8 +9590,12 @@
         <v>98.4</v>
       </c>
       <c r="G144" s="5">
-        <f t="shared" si="2"/>
+        <f>F144-E144</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H144" s="3">
+        <f>IF(F144&gt;50, G144*0.2, G144*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I144" t="s">
         <v>43</v>
@@ -5483,8 +9627,12 @@
         <v>124</v>
       </c>
       <c r="G145" s="5">
-        <f t="shared" si="2"/>
+        <f>F145-E145</f>
         <v>64</v>
+      </c>
+      <c r="H145" s="3">
+        <f>IF(F145&gt;50, G145*0.2, G145*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I145" t="s">
         <v>43</v>
@@ -5516,8 +9664,12 @@
         <v>87</v>
       </c>
       <c r="G146" s="5">
-        <f t="shared" si="2"/>
+        <f>F146-E146</f>
         <v>42</v>
+      </c>
+      <c r="H146" s="3">
+        <f>IF(F146&gt;50, G146*0.2, G146*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I146" t="s">
         <v>43</v>
@@ -5549,8 +9701,12 @@
         <v>502</v>
       </c>
       <c r="G147" s="5">
-        <f t="shared" si="2"/>
+        <f>F147-E147</f>
         <v>158</v>
+      </c>
+      <c r="H147" s="3">
+        <f>IF(F147&gt;50, G147*0.2, G147*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I147" t="s">
         <v>43</v>
@@ -5582,8 +9738,12 @@
         <v>98.4</v>
       </c>
       <c r="G148" s="5">
-        <f t="shared" si="2"/>
+        <f>F148-E148</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H148" s="3">
+        <f>IF(F148&gt;50, G148*0.2, G148*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I148" t="s">
         <v>37</v>
@@ -5615,8 +9775,12 @@
         <v>7</v>
       </c>
       <c r="G149" s="5">
-        <f t="shared" si="2"/>
+        <f>F149-E149</f>
         <v>3</v>
+      </c>
+      <c r="H149" s="3">
+        <f>IF(F149&gt;50, G149*0.2, G149*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I149" t="s">
         <v>41</v>
@@ -5648,8 +9812,12 @@
         <v>502</v>
       </c>
       <c r="G150" s="5">
-        <f t="shared" si="2"/>
+        <f>F150-E150</f>
         <v>158</v>
+      </c>
+      <c r="H150" s="3">
+        <f>IF(F150&gt;50, G150*0.2, G150*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I150" t="s">
         <v>37</v>
@@ -5681,8 +9849,12 @@
         <v>124</v>
       </c>
       <c r="G151" s="5">
-        <f t="shared" si="2"/>
+        <f>F151-E151</f>
         <v>64</v>
+      </c>
+      <c r="H151" s="3">
+        <f>IF(F151&gt;50, G151*0.2, G151*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I151" t="s">
         <v>41</v>
@@ -5714,8 +9886,12 @@
         <v>124</v>
       </c>
       <c r="G152" s="5">
-        <f t="shared" si="2"/>
+        <f>F152-E152</f>
         <v>64</v>
+      </c>
+      <c r="H152" s="3">
+        <f>IF(F152&gt;50, G152*0.2, G152*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I152" t="s">
         <v>39</v>
@@ -5747,8 +9923,12 @@
         <v>87</v>
       </c>
       <c r="G153" s="5">
-        <f t="shared" si="2"/>
+        <f>F153-E153</f>
         <v>42</v>
+      </c>
+      <c r="H153" s="3">
+        <f>IF(F153&gt;50, G153*0.2, G153*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I153" t="s">
         <v>37</v>
@@ -5780,8 +9960,12 @@
         <v>502</v>
       </c>
       <c r="G154" s="5">
-        <f t="shared" si="2"/>
+        <f>F154-E154</f>
         <v>158</v>
+      </c>
+      <c r="H154" s="3">
+        <f>IF(F154&gt;50, G154*0.2, G154*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I154" t="s">
         <v>41</v>
@@ -5813,8 +9997,12 @@
         <v>98.4</v>
       </c>
       <c r="G155" s="5">
-        <f t="shared" si="2"/>
+        <f>F155-E155</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H155" s="3">
+        <f>IF(F155&gt;50, G155*0.2, G155*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I155" t="s">
         <v>39</v>
@@ -5846,8 +10034,12 @@
         <v>87</v>
       </c>
       <c r="G156" s="5">
-        <f t="shared" si="2"/>
+        <f>F156-E156</f>
         <v>42</v>
+      </c>
+      <c r="H156" s="3">
+        <f>IF(F156&gt;50, G156*0.2, G156*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I156" t="s">
         <v>41</v>
@@ -5879,8 +10071,12 @@
         <v>124</v>
       </c>
       <c r="G157" s="5">
-        <f t="shared" si="2"/>
+        <f>F157-E157</f>
         <v>64</v>
+      </c>
+      <c r="H157" s="3">
+        <f>IF(F157&gt;50, G157*0.2, G157*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I157" t="s">
         <v>41</v>
@@ -5912,8 +10108,12 @@
         <v>7</v>
       </c>
       <c r="G158" s="5">
-        <f t="shared" si="2"/>
+        <f>F158-E158</f>
         <v>3</v>
+      </c>
+      <c r="H158" s="3">
+        <f>IF(F158&gt;50, G158*0.2, G158*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I158" t="s">
         <v>41</v>
@@ -5945,8 +10145,12 @@
         <v>502</v>
       </c>
       <c r="G159" s="5">
-        <f t="shared" si="2"/>
+        <f>F159-E159</f>
         <v>158</v>
+      </c>
+      <c r="H159" s="3">
+        <f>IF(F159&gt;50, G159*0.2, G159*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I159" t="s">
         <v>37</v>
@@ -5978,8 +10182,12 @@
         <v>77</v>
       </c>
       <c r="G160" s="5">
-        <f t="shared" si="2"/>
+        <f>F160-E160</f>
         <v>35</v>
+      </c>
+      <c r="H160" s="3">
+        <f>IF(F160&gt;50, G160*0.2, G160*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I160" t="s">
         <v>41</v>
@@ -6011,8 +10219,12 @@
         <v>98.4</v>
       </c>
       <c r="G161" s="5">
-        <f t="shared" si="2"/>
+        <f>F161-E161</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H161" s="3">
+        <f>IF(F161&gt;50, G161*0.2, G161*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I161" t="s">
         <v>43</v>
@@ -6044,8 +10256,12 @@
         <v>87</v>
       </c>
       <c r="G162" s="5">
-        <f t="shared" si="2"/>
+        <f>F162-E162</f>
         <v>42</v>
+      </c>
+      <c r="H162" s="3">
+        <f>IF(F162&gt;50, G162*0.2, G162*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I162" t="s">
         <v>39</v>
@@ -6077,8 +10293,12 @@
         <v>7</v>
       </c>
       <c r="G163" s="5">
-        <f t="shared" si="2"/>
+        <f>F163-E163</f>
         <v>3</v>
+      </c>
+      <c r="H163" s="3">
+        <f>IF(F163&gt;50, G163*0.2, G163*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I163" t="s">
         <v>37</v>
@@ -6110,8 +10330,12 @@
         <v>7</v>
       </c>
       <c r="G164" s="5">
-        <f t="shared" si="2"/>
+        <f>F164-E164</f>
         <v>3</v>
+      </c>
+      <c r="H164" s="3">
+        <f>IF(F164&gt;50, G164*0.2, G164*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I164" t="s">
         <v>41</v>
@@ -6143,8 +10367,12 @@
         <v>98.4</v>
       </c>
       <c r="G165" s="5">
-        <f t="shared" si="2"/>
+        <f>F165-E165</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H165" s="3">
+        <f>IF(F165&gt;50, G165*0.2, G165*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I165" t="s">
         <v>41</v>
@@ -6176,8 +10404,12 @@
         <v>98.4</v>
       </c>
       <c r="G166" s="5">
-        <f t="shared" si="2"/>
+        <f>F166-E166</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H166" s="3">
+        <f>IF(F166&gt;50, G166*0.2, G166*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I166" t="s">
         <v>41</v>
@@ -6209,8 +10441,12 @@
         <v>502</v>
       </c>
       <c r="G167" s="5">
-        <f t="shared" si="2"/>
+        <f>F167-E167</f>
         <v>158</v>
+      </c>
+      <c r="H167" s="3">
+        <f>IF(F167&gt;50, G167*0.2, G167*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I167" t="s">
         <v>41</v>
@@ -6242,8 +10478,12 @@
         <v>124</v>
       </c>
       <c r="G168" s="5">
-        <f t="shared" si="2"/>
+        <f>F168-E168</f>
         <v>64</v>
+      </c>
+      <c r="H168" s="3">
+        <f>IF(F168&gt;50, G168*0.2, G168*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I168" t="s">
         <v>41</v>
@@ -6275,8 +10515,12 @@
         <v>98.4</v>
       </c>
       <c r="G169" s="5">
-        <f t="shared" si="2"/>
+        <f>F169-E169</f>
         <v>40.100000000000009</v>
+      </c>
+      <c r="H169" s="3">
+        <f>IF(F169&gt;50, G169*0.2, G169*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I169" t="s">
         <v>41</v>
@@ -6308,8 +10552,12 @@
         <v>502</v>
       </c>
       <c r="G170" s="5">
-        <f t="shared" si="2"/>
+        <f>F170-E170</f>
         <v>158</v>
+      </c>
+      <c r="H170" s="3">
+        <f>IF(F170&gt;50, G170*0.2, G170*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I170" t="s">
         <v>41</v>
@@ -6341,8 +10589,12 @@
         <v>87</v>
       </c>
       <c r="G171" s="5">
-        <f t="shared" si="2"/>
+        <f>F171-E171</f>
         <v>42</v>
+      </c>
+      <c r="H171" s="3">
+        <f>IF(F171&gt;50, G171*0.2, G171*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I171" t="s">
         <v>37</v>
@@ -6374,8 +10626,12 @@
         <v>87</v>
       </c>
       <c r="G172" s="5">
-        <f t="shared" si="2"/>
+        <f>F172-E172</f>
         <v>42</v>
+      </c>
+      <c r="H172" s="3">
+        <f>IF(F172&gt;50, G172*0.2, G172*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I172" t="s">
         <v>39</v>
@@ -6385,6 +10641,33 @@
       </c>
       <c r="K172" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>47</v>
+      </c>
+      <c r="F174" s="5">
+        <f>SUM(F2:F172)</f>
+        <v>17110.599999999995</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>48</v>
+      </c>
+      <c r="F175" s="3">
+        <f>SUMIF(F2:F172, "&gt;50")</f>
+        <v>16088.399999999994</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>49</v>
+      </c>
+      <c r="F176" s="3">
+        <f>SUMIF(F2:F172, "&lt;=50")</f>
+        <v>1022.1999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -6395,6 +10678,9 @@
   </dataConsolidate>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
